--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121278682</v>
+        <v>121278778</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>8432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rustorp, Vstm</t>
+          <t>Storhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489812</v>
+        <v>489438</v>
       </c>
       <c r="R11" t="n">
-        <v>6645380</v>
+        <v>6645523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Engström</t>
+          <t>Johan Engström, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121278778</v>
+        <v>121278682</v>
       </c>
       <c r="B12" t="n">
-        <v>8432</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhöjden, Vstm</t>
+          <t>Rustorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489438</v>
+        <v>489812</v>
       </c>
       <c r="R12" t="n">
-        <v>6645523</v>
+        <v>6645380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Engström, Billy Lindblom</t>
+          <t>Johan Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1946,7 +1946,7 @@
         <v>121278748</v>
       </c>
       <c r="B13" t="n">
-        <v>91975</v>
+        <v>91985</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121278777</v>
+        <v>121278778</v>
       </c>
       <c r="B10" t="n">
         <v>8432</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489449</v>
+        <v>489438</v>
       </c>
       <c r="R10" t="n">
-        <v>6645360</v>
+        <v>6645523</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121278778</v>
+        <v>121278682</v>
       </c>
       <c r="B11" t="n">
-        <v>8432</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhöjden, Vstm</t>
+          <t>Rustorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489438</v>
+        <v>489812</v>
       </c>
       <c r="R11" t="n">
-        <v>6645523</v>
+        <v>6645380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Engström, Billy Lindblom</t>
+          <t>Johan Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121278682</v>
+        <v>121278748</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>91985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rustorp, Vstm</t>
+          <t>Storhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489812</v>
+        <v>489439</v>
       </c>
       <c r="R12" t="n">
-        <v>6645380</v>
+        <v>6645499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Engström</t>
+          <t>Johan Engström, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121278748</v>
+        <v>121278777</v>
       </c>
       <c r="B13" t="n">
-        <v>91985</v>
+        <v>8432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489439</v>
+        <v>489449</v>
       </c>
       <c r="R13" t="n">
-        <v>6645499</v>
+        <v>6645360</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121278778</v>
+        <v>121278777</v>
       </c>
       <c r="B10" t="n">
         <v>8432</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489438</v>
+        <v>489449</v>
       </c>
       <c r="R10" t="n">
-        <v>6645523</v>
+        <v>6645360</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,7 +1714,7 @@
         <v>121278682</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121278748</v>
+        <v>121278778</v>
       </c>
       <c r="B12" t="n">
-        <v>91985</v>
+        <v>8432</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489439</v>
+        <v>489438</v>
       </c>
       <c r="R12" t="n">
-        <v>6645499</v>
+        <v>6645523</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121278777</v>
+        <v>121278748</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
+        <v>91997</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489449</v>
+        <v>489439</v>
       </c>
       <c r="R13" t="n">
-        <v>6645360</v>
+        <v>6645499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121278777</v>
+        <v>121278778</v>
       </c>
       <c r="B10" t="n">
         <v>8432</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489449</v>
+        <v>489438</v>
       </c>
       <c r="R10" t="n">
-        <v>6645360</v>
+        <v>6645523</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121278778</v>
+        <v>121278777</v>
       </c>
       <c r="B12" t="n">
         <v>8432</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489438</v>
+        <v>489449</v>
       </c>
       <c r="R12" t="n">
-        <v>6645523</v>
+        <v>6645360</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,7 +1946,7 @@
         <v>121278748</v>
       </c>
       <c r="B13" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1598,7 +1598,7 @@
         <v>121278778</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
+        <v>8435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Engström, Billy Lindblom</t>
+          <t>Billy Lindblom, Johan Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1714,7 +1714,7 @@
         <v>121278682</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>121278777</v>
       </c>
       <c r="B12" t="n">
-        <v>8432</v>
+        <v>8435</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Engström, Billy Lindblom</t>
+          <t>Billy Lindblom, Johan Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1946,7 +1946,7 @@
         <v>121278748</v>
       </c>
       <c r="B13" t="n">
-        <v>91998</v>
+        <v>92001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121278778</v>
+        <v>121278682</v>
       </c>
       <c r="B10" t="n">
-        <v>8435</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhöjden, Vstm</t>
+          <t>Rustorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489438</v>
+        <v>489812</v>
       </c>
       <c r="R10" t="n">
-        <v>6645523</v>
+        <v>6645380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Johan Engström</t>
+          <t>Johan Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121278682</v>
+        <v>121278748</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>92001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rustorp, Vstm</t>
+          <t>Storhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489812</v>
+        <v>489439</v>
       </c>
       <c r="R11" t="n">
-        <v>6645380</v>
+        <v>6645499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Engström</t>
+          <t>Johan Engström, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Johan Engström</t>
+          <t>Johan Engström, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121278748</v>
+        <v>121278778</v>
       </c>
       <c r="B13" t="n">
-        <v>92001</v>
+        <v>8435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489439</v>
+        <v>489438</v>
       </c>
       <c r="R13" t="n">
-        <v>6645499</v>
+        <v>6645523</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121278682</v>
+        <v>121278777</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>8435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rustorp, Vstm</t>
+          <t>Storhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489812</v>
+        <v>489449</v>
       </c>
       <c r="R10" t="n">
-        <v>6645380</v>
+        <v>6645360</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Engström</t>
+          <t>Johan Engström, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121278748</v>
+        <v>121278778</v>
       </c>
       <c r="B11" t="n">
-        <v>92001</v>
+        <v>8435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489439</v>
+        <v>489438</v>
       </c>
       <c r="R11" t="n">
-        <v>6645499</v>
+        <v>6645523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121278777</v>
+        <v>121278682</v>
       </c>
       <c r="B12" t="n">
-        <v>8435</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhöjden, Vstm</t>
+          <t>Rustorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489449</v>
+        <v>489812</v>
       </c>
       <c r="R12" t="n">
-        <v>6645360</v>
+        <v>6645380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Engström, Billy Lindblom</t>
+          <t>Johan Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121278778</v>
+        <v>121278748</v>
       </c>
       <c r="B13" t="n">
-        <v>8435</v>
+        <v>92007</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489438</v>
+        <v>489439</v>
       </c>
       <c r="R13" t="n">
-        <v>6645523</v>
+        <v>6645499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121278777</v>
+        <v>121278748</v>
       </c>
       <c r="B10" t="n">
-        <v>8435</v>
+        <v>92008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489449</v>
+        <v>489439</v>
       </c>
       <c r="R10" t="n">
-        <v>6645360</v>
+        <v>6645499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121278778</v>
+        <v>121278682</v>
       </c>
       <c r="B11" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhöjden, Vstm</t>
+          <t>Rustorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489438</v>
+        <v>489812</v>
       </c>
       <c r="R11" t="n">
-        <v>6645523</v>
+        <v>6645380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Engström, Billy Lindblom</t>
+          <t>Johan Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121278682</v>
+        <v>121278778</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>8435</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rustorp, Vstm</t>
+          <t>Storhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489812</v>
+        <v>489438</v>
       </c>
       <c r="R12" t="n">
-        <v>6645380</v>
+        <v>6645523</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Engström</t>
+          <t>Johan Engström, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121278748</v>
+        <v>121278777</v>
       </c>
       <c r="B13" t="n">
-        <v>92007</v>
+        <v>8435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489439</v>
+        <v>489449</v>
       </c>
       <c r="R13" t="n">
-        <v>6645499</v>
+        <v>6645360</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121278748</v>
+        <v>121278682</v>
       </c>
       <c r="B10" t="n">
-        <v>92008</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhöjden, Vstm</t>
+          <t>Rustorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489439</v>
+        <v>489812</v>
       </c>
       <c r="R10" t="n">
-        <v>6645499</v>
+        <v>6645380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Engström, Billy Lindblom</t>
+          <t>Johan Engström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121278682</v>
+        <v>121278778</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rustorp, Vstm</t>
+          <t>Storhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489812</v>
+        <v>489438</v>
       </c>
       <c r="R11" t="n">
-        <v>6645380</v>
+        <v>6645523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Engström</t>
+          <t>Johan Engström, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121278778</v>
+        <v>121278777</v>
       </c>
       <c r="B12" t="n">
         <v>8435</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489438</v>
+        <v>489449</v>
       </c>
       <c r="R12" t="n">
-        <v>6645523</v>
+        <v>6645360</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121278777</v>
+        <v>121278748</v>
       </c>
       <c r="B13" t="n">
-        <v>8435</v>
+        <v>92008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489449</v>
+        <v>489439</v>
       </c>
       <c r="R13" t="n">
-        <v>6645360</v>
+        <v>6645499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121278778</v>
+        <v>121278748</v>
       </c>
       <c r="B11" t="n">
-        <v>8435</v>
+        <v>92008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489438</v>
+        <v>489439</v>
       </c>
       <c r="R11" t="n">
-        <v>6645523</v>
+        <v>6645499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121278748</v>
+        <v>121278778</v>
       </c>
       <c r="B13" t="n">
-        <v>92008</v>
+        <v>8435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489439</v>
+        <v>489438</v>
       </c>
       <c r="R13" t="n">
-        <v>6645499</v>
+        <v>6645523</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 48004-2019 artfynd.xlsx
+++ b/artfynd/A 48004-2019 artfynd.xlsx
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121278682</v>
+        <v>121278748</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>92008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rustorp, Vstm</t>
+          <t>Storhöjden, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489812</v>
+        <v>489439</v>
       </c>
       <c r="R10" t="n">
-        <v>6645380</v>
+        <v>6645499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Engström</t>
+          <t>Johan Engström, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121278748</v>
+        <v>121278778</v>
       </c>
       <c r="B11" t="n">
-        <v>92008</v>
+        <v>8435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489439</v>
+        <v>489438</v>
       </c>
       <c r="R11" t="n">
-        <v>6645499</v>
+        <v>6645523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121278778</v>
+        <v>121278682</v>
       </c>
       <c r="B13" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,38 +1955,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storhöjden, Vstm</t>
+          <t>Rustorp, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489438</v>
+        <v>489812</v>
       </c>
       <c r="R13" t="n">
-        <v>6645523</v>
+        <v>6645380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Engström, Billy Lindblom</t>
+          <t>Johan Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
